--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R37" t="n">
-        <v>0.6225832098024481</v>
+        <v>0.6403713015110895</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O38" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R37" t="n">
-        <v>0.6403713015110895</v>
+        <v>0.6581593932197309</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O38" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O37" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="R37" t="n">
-        <v>0.6581593932197309</v>
+        <v>0.7293117600542963</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O38" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="O37" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="R37" t="n">
-        <v>0.7293117600542963</v>
+        <v>0.8360403103061447</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="O38" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R48" t="n">
-        <v>0.3557618341728275</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O37" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8360403103061447</v>
+        <v>0.8538284020147859</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O38" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O48" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R48" t="n">
-        <v>0.3735499258814688</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O37" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8538284020147859</v>
+        <v>0.9071926771407101</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O38" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="O48" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="R48" t="n">
-        <v>0.426914201007393</v>
+        <v>0.7826760351802206</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="O49" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -8626,13 +8626,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>475</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O48" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="R48" t="n">
-        <v>0.7826760351802206</v>
+        <v>0.9249807688493514</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O49" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -8626,13 +8626,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R51" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8947,6 +8947,399 @@
         </is>
       </c>
       <c r="BC52" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -8985,7 +9378,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9461,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -9078,7 +9471,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -9098,7 +9491,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -9130,7 +9523,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -8626,13 +8626,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O51" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O52" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2477,6 +2522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2622,6 +2672,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2767,6 +2822,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2912,6 +2972,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3057,6 +3122,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3202,6 +3272,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3347,6 +3422,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3492,6 +3572,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3637,6 +3722,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4178,6 +4268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4323,6 +4418,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4468,6 +4568,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4613,6 +4718,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4758,6 +4868,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4903,6 +5018,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5048,6 +5168,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5193,6 +5318,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5338,6 +5468,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5876,6 +6011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6021,6 +6161,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6166,6 +6311,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6311,6 +6461,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6456,6 +6611,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6601,6 +6761,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6746,6 +6911,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6891,6 +7061,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7036,6 +7211,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7574,6 +7754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7719,6 +7904,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7864,6 +8054,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8009,6 +8204,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8154,6 +8354,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8299,6 +8504,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8444,6 +8654,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8589,6 +8804,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8734,6 +8954,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9272,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9417,6 +9647,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9562,6 +9797,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9707,6 +9947,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9852,6 +10097,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9997,6 +10247,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10142,6 +10397,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10287,6 +10547,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10432,6 +10697,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10970,6 +11240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11115,6 +11390,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11260,6 +11540,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11405,6 +11690,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11550,6 +11840,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11695,6 +11990,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11840,6 +12140,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11985,6 +12290,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12130,6 +12440,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12668,6 +12983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12813,6 +13133,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12958,6 +13283,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13103,6 +13433,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13248,6 +13583,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13393,6 +13733,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13538,6 +13883,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13683,6 +14033,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13828,6 +14183,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13960,13 +14320,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="O88" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="R88" t="n">
-        <v>0.9249807688493514</v>
+        <v>1.156225961061689</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -14119,10 +14479,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="O89" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -14366,6 +14726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14511,6 +14876,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14656,6 +15026,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14801,6 +15176,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14946,6 +15326,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15091,6 +15476,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15236,6 +15626,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15381,6 +15776,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15526,6 +15926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15658,13 +16063,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="R99" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -15817,10 +16222,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -16555,7 +16960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>518</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -14320,13 +14320,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O88" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R88" t="n">
-        <v>1.156225961061689</v>
+        <v>1.174014052770331</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O89" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O99" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R99" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.4624903844246757</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16222,10 +16222,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O100" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -14320,13 +14320,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O88" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R88" t="n">
-        <v>1.174014052770331</v>
+        <v>1.209590236187614</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O89" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R99" t="n">
-        <v>0.4624903844246757</v>
+        <v>0.4802784761333171</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16222,10 +16222,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O100" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -11497,13 +11497,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O81" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R81" t="n">
-        <v>1.245166419604896</v>
+        <v>1.316318786439462</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -12856,13 +12856,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O91" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R91" t="n">
-        <v>0.6225832098024481</v>
+        <v>0.6937355766370136</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -13000,13 +13000,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -12856,13 +12856,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O91" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R91" t="n">
-        <v>0.6937355766370136</v>
+        <v>0.7648879434715791</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -12961,117 +12961,252 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>D153</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Non-tuberculous mycobacterial infection</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>非结核分枝杆菌感染</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N92" t="n">
-        <v>2</v>
-      </c>
-      <c r="O92" t="n">
-        <v>2</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.03557618341728275</v>
-      </c>
-      <c r="U92" t="inlineStr">
+      <c r="N93" t="n">
+        <v>7</v>
+      </c>
+      <c r="O93" t="n">
+        <v>7</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="U93" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2015</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AO92" t="inlineStr">
+      <c r="AO93" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP92" t="inlineStr">
+      <c r="AP93" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS92" t="inlineStr">
+      <c r="AS93" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2015</t>
         </is>
       </c>
-      <c r="AT92" t="n">
+      <c r="AT93" t="n">
         <v>1</v>
       </c>
-      <c r="AV92" t="inlineStr">
+      <c r="AV93" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW92" t="inlineStr">
+      <c r="AW93" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
+      <c r="AX93" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY92" t="inlineStr">
+      <c r="AY93" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA92" t="inlineStr">
+      <c r="BA93" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB92" t="inlineStr">
+      <c r="BB93" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC92" t="inlineStr">
+      <c r="BC93" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -13193,7 +13328,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -13203,7 +13338,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -13255,7 +13390,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>569</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -1986,6 +1986,11 @@
       <c r="R11" t="n">
         <v>1.191802144478972</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2015</t>
@@ -2003,7 +2008,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2013,6 +2023,11 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2078,17 +2093,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2113,83 +2128,179 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>1</v>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2332,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2263,6 +2374,9 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
@@ -2294,12 +2408,12 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2314,12 +2428,12 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -2356,12 +2470,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2429,7 +2543,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2449,7 +2563,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -2491,12 +2605,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2564,7 +2678,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2584,7 +2698,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -2626,12 +2740,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2699,7 +2813,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2719,7 +2833,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -2761,12 +2875,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2834,7 +2948,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2854,7 +2968,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -2896,12 +3010,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2969,7 +3083,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2989,7 +3103,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -3031,12 +3145,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3104,7 +3218,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -3124,7 +3238,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -3166,12 +3280,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3239,7 +3353,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -3259,7 +3373,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -3301,12 +3415,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3340,18 +3454,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.102861685935765</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3360,7 +3469,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -3368,52 +3477,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3550,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3475,25 +3580,32 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.102861685935765</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3502,56 +3614,70 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -3578,17 +3704,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3613,80 +3739,179 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -3718,12 +3943,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3760,6 +3985,9 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
@@ -3791,12 +4019,12 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3811,12 +4039,12 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -3853,12 +4081,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3926,7 +4154,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3946,7 +4174,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -3988,12 +4216,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4061,7 +4289,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -4081,7 +4309,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -4123,12 +4351,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4196,7 +4424,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4216,7 +4444,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -4258,12 +4486,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4331,7 +4559,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4351,7 +4579,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -4393,12 +4621,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4466,7 +4694,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -4486,7 +4714,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -4528,12 +4756,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4601,7 +4829,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4621,7 +4849,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -4663,12 +4891,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4702,18 +4930,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.209590236187614</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4722,7 +4945,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
@@ -4730,52 +4953,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4807,12 +5026,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4837,12 +5056,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -4880,12 +5099,12 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4900,12 +5119,12 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -4942,12 +5161,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4972,22 +5191,32 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.209590236187614</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4996,56 +5225,70 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -5072,17 +5315,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5107,80 +5350,179 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -5212,12 +5554,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5285,12 +5627,12 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5305,12 +5647,12 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -5347,12 +5689,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5420,7 +5762,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -5440,7 +5782,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -5482,12 +5824,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5555,7 +5897,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -5575,7 +5917,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -5617,12 +5959,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5690,7 +6032,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5710,7 +6052,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -5752,12 +6094,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5825,7 +6167,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5845,7 +6187,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -5887,12 +6229,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5960,7 +6302,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5980,7 +6322,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6022,12 +6364,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6061,18 +6403,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.209590236187614</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6081,7 +6418,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
@@ -6089,52 +6426,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6499,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6196,12 +6529,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6239,12 +6572,12 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -6259,12 +6592,12 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -6301,12 +6634,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6331,12 +6664,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6374,7 +6707,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -6394,7 +6727,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -6436,12 +6769,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6466,22 +6799,32 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.209590236187614</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6490,56 +6833,70 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6923,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6601,80 +6958,179 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -6706,12 +7162,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6779,12 +7235,12 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -6799,12 +7255,12 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -6841,12 +7297,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6914,7 +7370,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -6934,7 +7390,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -6976,12 +7432,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7049,7 +7505,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -7069,7 +7525,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -7111,12 +7567,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7184,7 +7640,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -7204,7 +7660,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -7246,12 +7702,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7319,7 +7775,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -7339,7 +7795,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -7381,12 +7837,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7420,18 +7876,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.29853069473082</v>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -7440,7 +7891,7 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
@@ -7448,52 +7899,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7972,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7555,12 +8002,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -7598,12 +8045,12 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -7618,12 +8065,12 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -7660,12 +8107,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7690,12 +8137,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -7733,7 +8180,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -7753,7 +8200,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -7795,12 +8242,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7825,12 +8272,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -7868,7 +8315,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -7888,7 +8335,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -7930,12 +8377,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7960,22 +8407,32 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.29853069473082</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -7984,56 +8441,70 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -8060,17 +8531,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8095,80 +8566,179 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -8200,12 +8770,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8273,12 +8843,12 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -8293,12 +8863,12 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -8335,12 +8905,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8408,7 +8978,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -8428,7 +8998,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -8470,12 +9040,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8543,7 +9113,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -8563,7 +9133,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -8605,12 +9175,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8678,7 +9248,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -8698,7 +9268,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -8740,12 +9310,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8779,18 +9349,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.156225961061689</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -8799,7 +9364,7 @@
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
@@ -8807,52 +9372,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8884,12 +9445,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8914,12 +9475,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -8957,12 +9518,12 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -8977,12 +9538,12 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -9019,12 +9580,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9049,12 +9610,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -9092,7 +9653,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -9112,7 +9673,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -9154,12 +9715,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9184,12 +9745,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -9227,7 +9788,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -9247,7 +9808,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -9289,12 +9850,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9319,12 +9880,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -9362,7 +9923,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -9382,7 +9943,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -9424,12 +9985,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9454,22 +10015,32 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.156225961061689</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -9478,56 +10049,70 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9554,17 +10139,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -9589,80 +10174,179 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
+        <v>1</v>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9694,12 +10378,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9767,12 +10451,12 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -9787,12 +10471,12 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -9829,12 +10513,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9902,7 +10586,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -9922,7 +10606,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -9964,12 +10648,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10037,7 +10721,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -10057,7 +10741,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -10099,12 +10783,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10138,18 +10822,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.9071926771407101</v>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -10158,7 +10837,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
@@ -10166,52 +10845,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10243,12 +10918,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10273,12 +10948,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -10316,12 +10991,12 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -10336,12 +11011,12 @@
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -10378,12 +11053,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10408,12 +11083,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -10451,7 +11126,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -10471,7 +11146,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -10513,12 +11188,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10543,12 +11218,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -10586,7 +11261,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -10606,7 +11281,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -10648,12 +11323,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -10678,12 +11353,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -10721,7 +11396,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -10741,7 +11416,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -10783,12 +11458,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -10813,12 +11488,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -10856,7 +11531,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -10876,7 +11551,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -10918,12 +11593,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10948,22 +11623,32 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>0.9071926771407101</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -10972,56 +11657,70 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11048,17 +11747,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11083,80 +11782,179 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11986,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11261,12 +12059,12 @@
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -11281,12 +12079,12 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -11323,12 +12121,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11396,7 +12194,7 @@
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -11416,7 +12214,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -11458,12 +12256,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11497,18 +12295,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.316318786439462</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
@@ -11517,7 +12310,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
@@ -11525,52 +12318,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11602,12 +12391,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -11632,12 +12421,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -11675,12 +12464,12 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -11695,12 +12484,12 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -11737,12 +12526,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -11767,12 +12556,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -11810,7 +12599,7 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -11830,7 +12619,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -11872,12 +12661,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -11902,12 +12691,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -11945,7 +12734,7 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -11965,7 +12754,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -12007,12 +12796,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12037,12 +12826,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -12080,7 +12869,7 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -12100,7 +12889,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -12142,12 +12931,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12172,12 +12961,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -12215,7 +13004,7 @@
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -12235,7 +13024,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -12277,12 +13066,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12307,12 +13096,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -12350,7 +13139,7 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -12370,7 +13159,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -12412,12 +13201,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -12442,22 +13231,32 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.316318786439462</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
@@ -12466,56 +13265,70 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12542,17 +13355,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -12577,80 +13390,179 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12682,12 +13594,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -12755,12 +13667,12 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -12775,12 +13687,12 @@
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
@@ -12817,12 +13729,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -12856,18 +13768,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.7648879434715791</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
@@ -12876,7 +13783,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
@@ -12884,52 +13791,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2015</t>
-        </is>
-      </c>
+      <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12961,12 +13864,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -12991,12 +13894,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -13034,12 +13937,12 @@
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -13054,12 +13957,12 @@
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
@@ -13096,117 +13999,1704 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>D153</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Non-tuberculous mycobacterial infection</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>非结核分枝杆菌感染</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>44</v>
+      </c>
+      <c r="O99" t="n">
+        <v>44</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.7826760351802206</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>44</v>
+      </c>
+      <c r="O100" t="n">
+        <v>44</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N93" t="n">
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
         <v>7</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O102" t="n">
         <v>7</v>
       </c>
-      <c r="R93" t="n">
+      <c r="R102" t="n">
         <v>0.1245166419604896</v>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2015</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AO93" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP93" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2015</t>
         </is>
       </c>
-      <c r="AT93" t="n">
+      <c r="AT102" t="n">
         <v>1</v>
       </c>
-      <c r="AV93" t="inlineStr">
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW93" t="inlineStr">
+      <c r="AW102" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
+      <c r="AX102" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY93" t="inlineStr">
+      <c r="AY102" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA93" t="inlineStr">
+      <c r="BA102" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB93" t="inlineStr">
+      <c r="BB102" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC93" t="inlineStr">
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>non-tuberculous-mycobacterial-infection</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D153</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Non-tuberculous mycobacterial infection</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>非结核分枝杆菌感染</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>7</v>
+      </c>
+      <c r="O103" t="n">
+        <v>7</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Atypical mycobacteria</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Distinct from the tuberculosis total and child rows.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2015</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -13338,7 +15828,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -13358,7 +15848,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -13368,7 +15858,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13390,7 +15880,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1041,6 +1071,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1053,12 +1088,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1176,6 +1221,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1188,12 +1238,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1311,6 +1371,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1323,12 +1388,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1446,6 +1521,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1458,12 +1538,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1581,6 +1671,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1593,12 +1688,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1716,6 +1821,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1728,12 +1838,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1851,6 +1971,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1863,12 +1988,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2382,6 +2517,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2394,12 +2534,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2517,6 +2667,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2529,12 +2684,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2652,6 +2817,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2664,12 +2834,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2787,6 +2967,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2799,12 +2984,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2922,6 +3117,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2934,12 +3134,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3057,6 +3267,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3069,12 +3284,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3192,6 +3417,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3204,12 +3434,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3327,6 +3567,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3339,12 +3584,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3462,6 +3717,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3474,12 +3734,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3993,6 +4263,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4005,12 +4280,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4128,6 +4413,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4140,12 +4430,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4263,6 +4563,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4275,12 +4580,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4398,6 +4713,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4410,12 +4730,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4533,6 +4863,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4545,12 +4880,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4668,6 +5013,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4680,12 +5030,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4803,6 +5163,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4815,12 +5180,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4938,6 +5313,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4950,12 +5330,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5073,6 +5463,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5085,12 +5480,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5601,6 +6006,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5613,12 +6023,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5736,6 +6156,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5748,12 +6173,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5871,6 +6306,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5883,12 +6323,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6006,6 +6456,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6018,12 +6473,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6141,6 +6606,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6153,12 +6623,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6276,6 +6756,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6288,12 +6773,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6411,6 +6906,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6423,12 +6923,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6546,6 +7056,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6558,12 +7073,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6681,6 +7206,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6693,12 +7223,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7209,6 +7749,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7221,12 +7766,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7344,6 +7899,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7356,12 +7916,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7479,6 +8049,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7491,12 +8066,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7614,6 +8199,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7626,12 +8216,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7749,6 +8349,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7761,12 +8366,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7884,6 +8499,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7896,12 +8516,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8019,6 +8649,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8031,12 +8666,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8154,6 +8799,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8166,12 +8816,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8289,6 +8949,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8301,12 +8966,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8817,6 +9492,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8829,12 +9509,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8952,6 +9642,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8964,12 +9659,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9087,6 +9792,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9099,12 +9809,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9222,6 +9942,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9234,12 +9959,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9357,6 +10092,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9369,12 +10109,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9492,6 +10242,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9504,12 +10259,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9627,6 +10392,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9639,12 +10409,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9762,6 +10542,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9774,12 +10559,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9897,6 +10692,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9909,12 +10709,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10425,6 +11235,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10437,12 +11252,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10560,6 +11385,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10572,12 +11402,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10695,6 +11535,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10707,12 +11552,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10830,6 +11685,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10842,12 +11702,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10965,6 +11835,11 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10977,12 +11852,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11100,6 +11985,11 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11112,12 +12002,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11235,6 +12135,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11247,12 +12152,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11370,6 +12285,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11382,12 +12302,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11505,6 +12435,11 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11517,12 +12452,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12033,6 +12978,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12045,12 +12995,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12168,6 +13128,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12180,12 +13145,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12303,6 +13278,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12315,12 +13295,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12438,6 +13428,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12450,12 +13445,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12573,6 +13578,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12585,12 +13595,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12708,6 +13728,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12720,12 +13745,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12843,6 +13878,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12855,12 +13895,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12978,6 +14028,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12990,12 +14045,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13113,6 +14178,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13125,12 +14195,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13641,6 +14721,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13653,12 +14738,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13776,6 +14871,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13788,12 +14888,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13911,6 +15021,11 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13923,12 +15038,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14046,6 +15171,11 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14058,12 +15188,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14181,6 +15321,11 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14193,12 +15338,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14316,6 +15471,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14328,12 +15488,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14451,6 +15621,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14463,12 +15638,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14586,6 +15771,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14598,12 +15788,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14721,6 +15921,11 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14733,12 +15938,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15249,6 +16464,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15261,12 +16481,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>

--- a/diseases/d153/2026-2029.xlsx
+++ b/diseases/d153/2026-2029.xlsx
@@ -14320,13 +14320,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O88" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="R88" t="n">
-        <v>1.316318786439462</v>
+        <v>1.369683061565386</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O89" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O99" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R99" t="n">
-        <v>0.7826760351802206</v>
+        <v>0.8182522185975032</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16222,10 +16222,10 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O100" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -16606,13 +16606,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R102" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -16765,10 +16765,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="16">
